--- a/artfynd/A 17195-2026 artfynd.xlsx
+++ b/artfynd/A 17195-2026 artfynd.xlsx
@@ -902,7 +902,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134051753</v>
+        <v>134051751</v>
       </c>
       <c r="B4" t="n">
         <v>96662</v>
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>587642</v>
+        <v>587601</v>
       </c>
       <c r="R4" t="n">
-        <v>6628837</v>
+        <v>6628814</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134051751</v>
+        <v>134051753</v>
       </c>
       <c r="B5" t="n">
         <v>96662</v>
@@ -1047,10 +1047,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>587601</v>
+        <v>587642</v>
       </c>
       <c r="R5" t="n">
-        <v>6628814</v>
+        <v>6628837</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1750,10 +1750,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134051748</v>
+        <v>134051784</v>
       </c>
       <c r="B12" t="n">
-        <v>92637</v>
+        <v>8449</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1761,21 +1761,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6031</v>
+        <v>106554</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1789,10 +1789,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>587590</v>
+        <v>587485</v>
       </c>
       <c r="R12" t="n">
-        <v>6628803</v>
+        <v>6628792</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1856,10 +1856,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134051784</v>
+        <v>134051748</v>
       </c>
       <c r="B13" t="n">
-        <v>8449</v>
+        <v>92637</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1867,21 +1867,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106554</v>
+        <v>6031</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1895,10 +1895,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>587485</v>
+        <v>587590</v>
       </c>
       <c r="R13" t="n">
-        <v>6628792</v>
+        <v>6628803</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1962,10 +1962,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134051738</v>
+        <v>134051790</v>
       </c>
       <c r="B14" t="n">
-        <v>93293</v>
+        <v>98046</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1973,26 +1973,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5964</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2001,10 +2001,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>588030</v>
+        <v>587573</v>
       </c>
       <c r="R14" t="n">
-        <v>6628918</v>
+        <v>6628721</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2031,12 +2031,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2068,10 +2068,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134051790</v>
+        <v>134051738</v>
       </c>
       <c r="B15" t="n">
-        <v>98046</v>
+        <v>93293</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2079,26 +2079,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>5964</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2107,10 +2107,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>587573</v>
+        <v>588030</v>
       </c>
       <c r="R15" t="n">
-        <v>6628721</v>
+        <v>6628918</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2137,12 +2137,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2492,10 +2492,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134051783</v>
+        <v>134051740</v>
       </c>
       <c r="B19" t="n">
-        <v>98046</v>
+        <v>87460</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2503,26 +2503,22 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>3624</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2531,10 +2527,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>587602</v>
+        <v>588044</v>
       </c>
       <c r="R19" t="n">
-        <v>6628740</v>
+        <v>6628906</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2561,12 +2557,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2598,10 +2594,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134051740</v>
+        <v>134051783</v>
       </c>
       <c r="B20" t="n">
-        <v>87460</v>
+        <v>98046</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2609,22 +2605,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3624</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2633,10 +2633,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>588044</v>
+        <v>587602</v>
       </c>
       <c r="R20" t="n">
-        <v>6628906</v>
+        <v>6628740</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2908,7 +2908,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134051731</v>
+        <v>134051736</v>
       </c>
       <c r="B23" t="n">
         <v>87460</v>
@@ -2934,7 +2934,7 @@
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2943,10 +2943,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>588131</v>
+        <v>587992</v>
       </c>
       <c r="R23" t="n">
-        <v>6628893</v>
+        <v>6628991</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3010,7 +3010,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134051736</v>
+        <v>134051731</v>
       </c>
       <c r="B24" t="n">
         <v>87460</v>
@@ -3036,7 +3036,7 @@
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3045,10 +3045,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>587992</v>
+        <v>588131</v>
       </c>
       <c r="R24" t="n">
-        <v>6628991</v>
+        <v>6628893</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 17195-2026 artfynd.xlsx
+++ b/artfynd/A 17195-2026 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>134051793</v>
       </c>
       <c r="B3" t="n">
-        <v>98046</v>
+        <v>98053</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134051751</v>
+        <v>134051753</v>
       </c>
       <c r="B4" t="n">
-        <v>96662</v>
+        <v>96669</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>587601</v>
+        <v>587642</v>
       </c>
       <c r="R4" t="n">
-        <v>6628814</v>
+        <v>6628837</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134051753</v>
+        <v>134051751</v>
       </c>
       <c r="B5" t="n">
-        <v>96662</v>
+        <v>96669</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1047,10 +1047,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>587642</v>
+        <v>587601</v>
       </c>
       <c r="R5" t="n">
-        <v>6628837</v>
+        <v>6628814</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1117,7 +1117,7 @@
         <v>134051747</v>
       </c>
       <c r="B6" t="n">
-        <v>92351</v>
+        <v>92358</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
         <v>134051792</v>
       </c>
       <c r="B8" t="n">
-        <v>98052</v>
+        <v>98059</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
         <v>134051799</v>
       </c>
       <c r="B9" t="n">
-        <v>101389</v>
+        <v>101396</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>134051781</v>
       </c>
       <c r="B10" t="n">
-        <v>98046</v>
+        <v>98053</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1750,10 +1750,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134051784</v>
+        <v>134051748</v>
       </c>
       <c r="B12" t="n">
-        <v>8449</v>
+        <v>92644</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1761,21 +1761,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106554</v>
+        <v>6031</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1789,10 +1789,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>587485</v>
+        <v>587590</v>
       </c>
       <c r="R12" t="n">
-        <v>6628792</v>
+        <v>6628803</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1856,10 +1856,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134051748</v>
+        <v>134051784</v>
       </c>
       <c r="B13" t="n">
-        <v>92637</v>
+        <v>8449</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1867,21 +1867,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6031</v>
+        <v>106554</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1895,10 +1895,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>587590</v>
+        <v>587485</v>
       </c>
       <c r="R13" t="n">
-        <v>6628803</v>
+        <v>6628792</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1962,10 +1962,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134051790</v>
+        <v>134051738</v>
       </c>
       <c r="B14" t="n">
-        <v>98046</v>
+        <v>93300</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1973,26 +1973,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>5964</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2001,10 +2001,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>587573</v>
+        <v>588030</v>
       </c>
       <c r="R14" t="n">
-        <v>6628721</v>
+        <v>6628918</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2031,12 +2031,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2068,10 +2068,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134051738</v>
+        <v>134051790</v>
       </c>
       <c r="B15" t="n">
-        <v>93293</v>
+        <v>98053</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2079,26 +2079,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5964</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2107,10 +2107,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>588030</v>
+        <v>587573</v>
       </c>
       <c r="R15" t="n">
-        <v>6628918</v>
+        <v>6628721</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2137,12 +2137,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2283,7 +2283,7 @@
         <v>134051782</v>
       </c>
       <c r="B17" t="n">
-        <v>96662</v>
+        <v>96669</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>134051737</v>
       </c>
       <c r="B18" t="n">
-        <v>93293</v>
+        <v>93300</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2492,10 +2492,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134051740</v>
+        <v>134051783</v>
       </c>
       <c r="B19" t="n">
-        <v>87460</v>
+        <v>98053</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2503,22 +2503,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3624</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2527,10 +2531,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>588044</v>
+        <v>587602</v>
       </c>
       <c r="R19" t="n">
-        <v>6628906</v>
+        <v>6628740</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2557,12 +2561,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2594,10 +2598,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134051783</v>
+        <v>134051740</v>
       </c>
       <c r="B20" t="n">
-        <v>98046</v>
+        <v>87467</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2605,26 +2609,22 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>3624</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2633,10 +2633,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>587602</v>
+        <v>588044</v>
       </c>
       <c r="R20" t="n">
-        <v>6628740</v>
+        <v>6628906</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2809,7 +2809,7 @@
         <v>134051734</v>
       </c>
       <c r="B22" t="n">
-        <v>87460</v>
+        <v>87467</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2908,10 +2908,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134051736</v>
+        <v>134051731</v>
       </c>
       <c r="B23" t="n">
-        <v>87460</v>
+        <v>87467</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2943,10 +2943,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>587992</v>
+        <v>588131</v>
       </c>
       <c r="R23" t="n">
-        <v>6628991</v>
+        <v>6628893</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3010,10 +3010,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134051731</v>
+        <v>134051736</v>
       </c>
       <c r="B24" t="n">
-        <v>87460</v>
+        <v>87467</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3045,10 +3045,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>588131</v>
+        <v>587992</v>
       </c>
       <c r="R24" t="n">
-        <v>6628893</v>
+        <v>6628991</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 17195-2026 artfynd.xlsx
+++ b/artfynd/A 17195-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AY54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,61 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>108773790</v>
+        <v>134051801</v>
       </c>
       <c r="B2" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79910</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>1352</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>Jatta</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nedåker, 1 km SSO om Tomta, Vstm</t>
+          <t>Tomta gård, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587352.5553530989</v>
+        <v>587335</v>
       </c>
       <c r="R2" t="n">
-        <v>6628859.658433634</v>
+        <v>6628849</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,22 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-05-04</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-05-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,29 +758,33 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AR2" t="inlineStr"/>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Thorleif Joelson</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Thorleif Joelson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Felix Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Tomta gård</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134051793</v>
+        <v>134051751</v>
       </c>
       <c r="B3" t="n">
-        <v>98053</v>
+        <v>96676</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,26 +792,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>2170</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -835,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587603</v>
+        <v>587601</v>
       </c>
       <c r="R3" t="n">
-        <v>6628695</v>
+        <v>6628814</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -905,7 +890,7 @@
         <v>134051753</v>
       </c>
       <c r="B4" t="n">
-        <v>96669</v>
+        <v>96676</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134051751</v>
+        <v>134051782</v>
       </c>
       <c r="B5" t="n">
-        <v>96669</v>
+        <v>96676</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1047,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>587601</v>
+        <v>587604</v>
       </c>
       <c r="R5" t="n">
-        <v>6628814</v>
+        <v>6628729</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1114,37 +1099,33 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134051747</v>
+        <v>134051731</v>
       </c>
       <c r="B6" t="n">
-        <v>92358</v>
+        <v>87474</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6040162</v>
+        <v>3624</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallkötticka</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1153,10 +1134,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>587590</v>
+        <v>588131</v>
       </c>
       <c r="R6" t="n">
-        <v>6628803</v>
+        <v>6628893</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,12 +1164,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,10 +1201,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134051749</v>
+        <v>134051734</v>
       </c>
       <c r="B7" t="n">
-        <v>8449</v>
+        <v>87474</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1231,26 +1212,22 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106554</v>
+        <v>3624</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1259,10 +1236,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>587595</v>
+        <v>588084</v>
       </c>
       <c r="R7" t="n">
-        <v>6628818</v>
+        <v>6628963</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1289,12 +1266,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1326,10 +1303,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134051792</v>
+        <v>134051736</v>
       </c>
       <c r="B8" t="n">
-        <v>98059</v>
+        <v>87474</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1337,26 +1314,22 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221941</v>
+        <v>3624</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1365,10 +1338,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>587603</v>
+        <v>587992</v>
       </c>
       <c r="R8" t="n">
-        <v>6628704</v>
+        <v>6628991</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1395,12 +1368,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1432,10 +1405,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134051799</v>
+        <v>134051740</v>
       </c>
       <c r="B9" t="n">
-        <v>101396</v>
+        <v>87474</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1443,26 +1416,22 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>3624</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1471,10 +1440,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>587330</v>
+        <v>588044</v>
       </c>
       <c r="R9" t="n">
-        <v>6628838</v>
+        <v>6628906</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1501,12 +1470,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1538,37 +1507,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134051781</v>
+        <v>134051737</v>
       </c>
       <c r="B10" t="n">
-        <v>98053</v>
+        <v>93307</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>5964</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1577,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>587645</v>
+        <v>588005</v>
       </c>
       <c r="R10" t="n">
-        <v>6628653</v>
+        <v>6628976</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1607,12 +1576,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1644,37 +1613,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134051724</v>
+        <v>134051738</v>
       </c>
       <c r="B11" t="n">
-        <v>8449</v>
+        <v>93307</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106554</v>
+        <v>5964</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1683,10 +1652,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>588167</v>
+        <v>588030</v>
       </c>
       <c r="R11" t="n">
-        <v>6628896</v>
+        <v>6628918</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1753,7 +1722,7 @@
         <v>134051748</v>
       </c>
       <c r="B12" t="n">
-        <v>92644</v>
+        <v>92651</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1856,10 +1825,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134051784</v>
+        <v>134051757</v>
       </c>
       <c r="B13" t="n">
-        <v>8449</v>
+        <v>57972</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1867,21 +1836,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1895,10 +1864,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>587485</v>
+        <v>587854</v>
       </c>
       <c r="R13" t="n">
-        <v>6628792</v>
+        <v>6628625</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1962,10 +1931,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134051738</v>
+        <v>134051717</v>
       </c>
       <c r="B14" t="n">
-        <v>93300</v>
+        <v>58250</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1973,38 +1942,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5964</v>
+        <v>103019</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Stjärtmes</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Aegithalos caudatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Tomta gård, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>588030</v>
+        <v>588613</v>
       </c>
       <c r="R14" t="n">
-        <v>6628918</v>
+        <v>6629135</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2026,7 +1991,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>Romfartuna</t>
+          <t>Kumla</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2068,32 +2033,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134051790</v>
+        <v>134051713</v>
       </c>
       <c r="B15" t="n">
-        <v>98053</v>
+        <v>58136</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2107,10 +2072,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>587573</v>
+        <v>588679</v>
       </c>
       <c r="R15" t="n">
-        <v>6628721</v>
+        <v>6629180</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2132,17 +2097,17 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>Romfartuna</t>
+          <t>Kumla</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2174,37 +2139,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134051746</v>
+        <v>134051762</v>
       </c>
       <c r="B16" t="n">
-        <v>8460</v>
+        <v>58136</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2213,10 +2178,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>587501</v>
+        <v>587706</v>
       </c>
       <c r="R16" t="n">
-        <v>6628885</v>
+        <v>6628822</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2280,32 +2245,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134051782</v>
+        <v>134051794</v>
       </c>
       <c r="B17" t="n">
-        <v>96669</v>
+        <v>58136</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2170</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2319,10 +2284,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>587604</v>
+        <v>587391</v>
       </c>
       <c r="R17" t="n">
-        <v>6628729</v>
+        <v>6628557</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2386,37 +2351,37 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134051737</v>
+        <v>134051808</v>
       </c>
       <c r="B18" t="n">
-        <v>93300</v>
+        <v>58136</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5964</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2425,10 +2390,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>588005</v>
+        <v>587572</v>
       </c>
       <c r="R18" t="n">
-        <v>6628976</v>
+        <v>6628728</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2455,12 +2420,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2492,37 +2457,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134051783</v>
+        <v>134051809</v>
       </c>
       <c r="B19" t="n">
-        <v>98053</v>
+        <v>58136</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2531,10 +2496,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>587602</v>
+        <v>587527</v>
       </c>
       <c r="R19" t="n">
-        <v>6628740</v>
+        <v>6628687</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2598,10 +2563,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134051740</v>
+        <v>134051746</v>
       </c>
       <c r="B20" t="n">
-        <v>87467</v>
+        <v>8460</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2609,19 +2574,23 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3624</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr">
         <is>
           <t>1</t>
@@ -2633,10 +2602,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>588044</v>
+        <v>587501</v>
       </c>
       <c r="R20" t="n">
-        <v>6628906</v>
+        <v>6628885</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2663,12 +2632,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2806,10 +2775,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134051734</v>
+        <v>134051722</v>
       </c>
       <c r="B22" t="n">
-        <v>87467</v>
+        <v>8449</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2817,22 +2786,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3624</v>
+        <v>106554</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2841,10 +2814,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>588084</v>
+        <v>588471</v>
       </c>
       <c r="R22" t="n">
-        <v>6628963</v>
+        <v>6629028</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2866,7 +2839,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>Romfartuna</t>
+          <t>Kumla</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -2908,10 +2881,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134051731</v>
+        <v>134051724</v>
       </c>
       <c r="B23" t="n">
-        <v>87467</v>
+        <v>8449</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2919,22 +2892,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3624</v>
+        <v>106554</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2943,10 +2920,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>588131</v>
+        <v>588167</v>
       </c>
       <c r="R23" t="n">
-        <v>6628893</v>
+        <v>6628896</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3010,10 +2987,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134051736</v>
+        <v>134051742</v>
       </c>
       <c r="B24" t="n">
-        <v>87467</v>
+        <v>8449</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3021,22 +2998,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3624</v>
+        <v>106554</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3045,10 +3026,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>587992</v>
+        <v>587994</v>
       </c>
       <c r="R24" t="n">
-        <v>6628991</v>
+        <v>6628666</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3112,32 +3093,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134051794</v>
+        <v>134051749</v>
       </c>
       <c r="B25" t="n">
-        <v>58136</v>
+        <v>8449</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>106554</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3151,10 +3132,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>587391</v>
+        <v>587595</v>
       </c>
       <c r="R25" t="n">
-        <v>6628557</v>
+        <v>6628818</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3218,37 +3199,37 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134051808</v>
+        <v>134051784</v>
       </c>
       <c r="B26" t="n">
-        <v>58136</v>
+        <v>8449</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>106554</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3257,10 +3238,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>587572</v>
+        <v>587485</v>
       </c>
       <c r="R26" t="n">
-        <v>6628728</v>
+        <v>6628792</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3324,32 +3305,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134051757</v>
+        <v>134051804</v>
       </c>
       <c r="B27" t="n">
-        <v>57972</v>
+        <v>8449</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3363,10 +3344,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>587854</v>
+        <v>587345</v>
       </c>
       <c r="R27" t="n">
-        <v>6628625</v>
+        <v>6628861</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3430,32 +3411,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134051713</v>
+        <v>134051811</v>
       </c>
       <c r="B28" t="n">
-        <v>58136</v>
+        <v>8449</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>106554</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3469,10 +3450,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>588679</v>
+        <v>587363</v>
       </c>
       <c r="R28" t="n">
-        <v>6629180</v>
+        <v>6628541</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3494,17 +3475,17 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>Kumla</t>
+          <t>Romfartuna</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3536,32 +3517,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134051809</v>
+        <v>134051812</v>
       </c>
       <c r="B29" t="n">
-        <v>58136</v>
+        <v>8449</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>106554</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3575,10 +3556,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>587527</v>
+        <v>587364</v>
       </c>
       <c r="R29" t="n">
-        <v>6628687</v>
+        <v>6628533</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3642,49 +3623,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134051762</v>
+        <v>134051743</v>
       </c>
       <c r="B30" t="n">
-        <v>58136</v>
+        <v>111153</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>220240</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Tomta gård, Vstm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>587706</v>
+        <v>587990</v>
       </c>
       <c r="R30" t="n">
-        <v>6628822</v>
+        <v>6628678</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3711,12 +3688,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3741,6 +3718,2542 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr">
+        <is>
+          <t>Tomta gård</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>134051785</v>
+      </c>
+      <c r="B31" t="n">
+        <v>111153</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Tomta gård, Vstm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>587459</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6628783</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Romfartuna</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR31" t="inlineStr"/>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Felix Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Felix Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Tomta gård</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>134051789</v>
+      </c>
+      <c r="B32" t="n">
+        <v>111153</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Tomta gård, Vstm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>587567</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6628724</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Romfartuna</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR32" t="inlineStr"/>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Felix Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Felix Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Tomta gård</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>134051791</v>
+      </c>
+      <c r="B33" t="n">
+        <v>111153</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Tomta gård, Vstm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>587603</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6628709</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Romfartuna</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR33" t="inlineStr"/>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Felix Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Felix Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Tomta gård</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>134051796</v>
+      </c>
+      <c r="B34" t="n">
+        <v>111153</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Tomta gård, Vstm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>587236</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6628757</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Romfartuna</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR34" t="inlineStr"/>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Felix Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Felix Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Tomta gård</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>134051792</v>
+      </c>
+      <c r="B35" t="n">
+        <v>98066</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Tomta gård, Vstm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>587603</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6628704</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Romfartuna</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR35" t="inlineStr"/>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Felix Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Felix Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Tomta gård</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>134051781</v>
+      </c>
+      <c r="B36" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Tomta gård, Vstm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>587645</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6628653</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Romfartuna</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR36" t="inlineStr"/>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Felix Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Felix Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Tomta gård</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>134051783</v>
+      </c>
+      <c r="B37" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Tomta gård, Vstm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>587602</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6628740</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Romfartuna</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR37" t="inlineStr"/>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Felix Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Felix Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Tomta gård</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>134051790</v>
+      </c>
+      <c r="B38" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Tomta gård, Vstm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>587573</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6628721</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Romfartuna</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR38" t="inlineStr"/>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Felix Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Felix Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>Tomta gård</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>134051793</v>
+      </c>
+      <c r="B39" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Tomta gård, Vstm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>587603</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6628695</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Romfartuna</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR39" t="inlineStr"/>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Felix Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Felix Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Tomta gård</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>134051716</v>
+      </c>
+      <c r="B40" t="n">
+        <v>103764</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>222004</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Kärrviol</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Viola palustris</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Tomta gård, Vstm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>588699</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6629217</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Kumla</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR40" t="inlineStr"/>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Felix Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Felix Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>Tomta gård</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>134051741</v>
+      </c>
+      <c r="B41" t="n">
+        <v>103764</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>222004</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Kärrviol</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Viola palustris</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Tomta gård, Vstm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>588014</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6628673</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Romfartuna</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR41" t="inlineStr"/>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Felix Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Felix Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>Tomta gård</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>108773790</v>
+      </c>
+      <c r="B42" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Nedåker, 1 km SSO om Tomta, Vstm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>587353</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6628860</v>
+      </c>
+      <c r="S42" t="n">
+        <v>25</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Romfartuna</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2023-05-04</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2023-05-04</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>134051799</v>
+      </c>
+      <c r="B43" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Tomta gård, Vstm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>587330</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6628838</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Romfartuna</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR43" t="inlineStr"/>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Felix Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Felix Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>Tomta gård</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>134051803</v>
+      </c>
+      <c r="B44" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Tomta gård, Vstm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>587336</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6628849</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Romfartuna</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR44" t="inlineStr"/>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Felix Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Felix Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Tomta gård</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>134051714</v>
+      </c>
+      <c r="B45" t="n">
+        <v>98277</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>222736</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Majbräken</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Athyrium filix-femina</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Tomta gård, Vstm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>588695</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6629212</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Kumla</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR45" t="inlineStr"/>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Felix Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Felix Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>Tomta gård</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>134051720</v>
+      </c>
+      <c r="B46" t="n">
+        <v>98277</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>222736</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Majbräken</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Athyrium filix-femina</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Tomta gård, Vstm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>588566</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6629136</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Romfartuna</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR46" t="inlineStr"/>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Felix Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Felix Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Tomta gård</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>134051723</v>
+      </c>
+      <c r="B47" t="n">
+        <v>98277</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>222736</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Majbräken</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Athyrium filix-femina</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Tomta gård, Vstm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>588471</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6629028</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Kumla</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR47" t="inlineStr"/>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Felix Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Felix Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Tomta gård</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>134051727</v>
+      </c>
+      <c r="B48" t="n">
+        <v>98277</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>222736</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Majbräken</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Athyrium filix-femina</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Tomta gård, Vstm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>588195</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6628895</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Romfartuna</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR48" t="inlineStr"/>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Felix Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Felix Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>Tomta gård</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>134051715</v>
+      </c>
+      <c r="B49" t="n">
+        <v>98249</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Tomta gård, Vstm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>588700</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6629214</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Kumla</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR49" t="inlineStr"/>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Felix Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Felix Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>Tomta gård</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>134051721</v>
+      </c>
+      <c r="B50" t="n">
+        <v>98249</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Tomta gård, Vstm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>588517</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6629078</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Kumla</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR50" t="inlineStr"/>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Felix Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Felix Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>Tomta gård</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>134051726</v>
+      </c>
+      <c r="B51" t="n">
+        <v>98249</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Tomta gård, Vstm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>588195</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6628895</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Romfartuna</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR51" t="inlineStr"/>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Felix Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Felix Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>Tomta gård</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>134051729</v>
+      </c>
+      <c r="B52" t="n">
+        <v>98249</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Tomta gård, Vstm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>588240</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6628909</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Romfartuna</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR52" t="inlineStr"/>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Felix Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Felix Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>Tomta gård</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>134051810</v>
+      </c>
+      <c r="B53" t="n">
+        <v>98249</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Tomta gård, Vstm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>587408</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6628529</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Romfartuna</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR53" t="inlineStr"/>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Felix Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Felix Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>Tomta gård</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>134051747</v>
+      </c>
+      <c r="B54" t="n">
+        <v>92365</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6040162</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Tallkötticka</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Leptoporus erubescens</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Tomta gård, Vstm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>587590</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6628803</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Romfartuna</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR54" t="inlineStr"/>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Felix Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Felix Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
         <is>
           <t>Tomta gård</t>
         </is>

--- a/artfynd/A 17195-2026 artfynd.xlsx
+++ b/artfynd/A 17195-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY54"/>
+  <dimension ref="A1:AZ54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Tomta gård</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134051801</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
           <t>Tomta gård</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134051751</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
           <t>Tomta gård</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134051753</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
           <t>Tomta gård</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134051782</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1198,6 +1223,11 @@
           <t>Tomta gård</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134051731</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1300,6 +1330,11 @@
           <t>Tomta gård</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134051734</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1402,6 +1437,11 @@
           <t>Tomta gård</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134051736</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1504,6 +1544,11 @@
           <t>Tomta gård</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134051740</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1610,6 +1655,11 @@
           <t>Tomta gård</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134051737</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1716,6 +1766,11 @@
           <t>Tomta gård</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134051738</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1822,6 +1877,11 @@
           <t>Tomta gård</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134051748</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1928,6 +1988,11 @@
           <t>Tomta gård</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134051757</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2030,6 +2095,11 @@
           <t>Tomta gård</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134051717</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2136,6 +2206,11 @@
           <t>Tomta gård</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134051713</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2242,6 +2317,11 @@
           <t>Tomta gård</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134051762</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2348,6 +2428,11 @@
           <t>Tomta gård</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134051794</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2454,6 +2539,11 @@
           <t>Tomta gård</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134051808</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2560,6 +2650,11 @@
           <t>Tomta gård</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134051809</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2666,6 +2761,11 @@
           <t>Tomta gård</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134051746</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2772,6 +2872,11 @@
           <t>Tomta gård</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134051788</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2878,6 +2983,11 @@
           <t>Tomta gård</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134051722</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2984,6 +3094,11 @@
           <t>Tomta gård</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134051724</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3090,6 +3205,11 @@
           <t>Tomta gård</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134051742</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3196,6 +3316,11 @@
           <t>Tomta gård</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134051749</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3302,6 +3427,11 @@
           <t>Tomta gård</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134051784</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3408,6 +3538,11 @@
           <t>Tomta gård</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134051804</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3514,6 +3649,11 @@
           <t>Tomta gård</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134051811</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3620,6 +3760,11 @@
           <t>Tomta gård</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134051812</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3722,6 +3867,11 @@
           <t>Tomta gård</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134051743</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3828,6 +3978,11 @@
           <t>Tomta gård</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134051785</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3934,6 +4089,11 @@
           <t>Tomta gård</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134051789</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4040,6 +4200,11 @@
           <t>Tomta gård</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134051791</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4146,6 +4311,11 @@
           <t>Tomta gård</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134051796</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4252,6 +4422,11 @@
           <t>Tomta gård</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134051792</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4358,6 +4533,11 @@
           <t>Tomta gård</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134051781</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4464,6 +4644,11 @@
           <t>Tomta gård</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134051783</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4570,6 +4755,11 @@
           <t>Tomta gård</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134051790</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4676,6 +4866,11 @@
           <t>Tomta gård</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134051793</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4782,6 +4977,11 @@
           <t>Tomta gård</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134051716</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4888,6 +5088,11 @@
           <t>Tomta gård</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134051741</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4994,6 +5199,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108773790</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5100,6 +5310,11 @@
           <t>Tomta gård</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134051799</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5206,6 +5421,11 @@
           <t>Tomta gård</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134051803</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5308,6 +5528,11 @@
           <t>Tomta gård</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134051714</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5414,6 +5639,11 @@
           <t>Tomta gård</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134051720</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5520,6 +5750,11 @@
           <t>Tomta gård</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134051723</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5626,6 +5861,11 @@
           <t>Tomta gård</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134051727</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5728,6 +5968,11 @@
           <t>Tomta gård</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134051715</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5834,6 +6079,11 @@
           <t>Tomta gård</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134051721</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5940,6 +6190,11 @@
           <t>Tomta gård</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134051726</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6046,6 +6301,11 @@
           <t>Tomta gård</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134051729</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6152,6 +6412,11 @@
           <t>Tomta gård</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134051810</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6258,8 +6523,68 @@
           <t>Tomta gård</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134051747</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>